--- a/templates/xlsx/unit-economics.xlsx
+++ b/templates/xlsx/unit-economics.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Economics" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -592,7 +592,7 @@
         <v/>
       </c>
       <c r="N2" s="8">
-        <f>IF(A2="","",IF(K2&lt;=0,"Drop",IF(J2&gt;=0.65,"Profit product",IF(J2&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A2="","",IF(K2&lt;=0,"Drop",IF(J2&gt;=0.6,"Profit product",IF(J2&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -625,7 +625,7 @@
         <v/>
       </c>
       <c r="N3" s="8">
-        <f>IF(A3="","",IF(K3&lt;=0,"Drop",IF(J3&gt;=0.65,"Profit product",IF(J3&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A3="","",IF(K3&lt;=0,"Drop",IF(J3&gt;=0.6,"Profit product",IF(J3&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -658,7 +658,7 @@
         <v/>
       </c>
       <c r="N4" s="8">
-        <f>IF(A4="","",IF(K4&lt;=0,"Drop",IF(J4&gt;=0.65,"Profit product",IF(J4&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A4="","",IF(K4&lt;=0,"Drop",IF(J4&gt;=0.6,"Profit product",IF(J4&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -691,7 +691,7 @@
         <v/>
       </c>
       <c r="N5" s="8">
-        <f>IF(A5="","",IF(K5&lt;=0,"Drop",IF(J5&gt;=0.65,"Profit product",IF(J5&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A5="","",IF(K5&lt;=0,"Drop",IF(J5&gt;=0.6,"Profit product",IF(J5&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -724,7 +724,7 @@
         <v/>
       </c>
       <c r="N6" s="8">
-        <f>IF(A6="","",IF(K6&lt;=0,"Drop",IF(J6&gt;=0.65,"Profit product",IF(J6&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A6="","",IF(K6&lt;=0,"Drop",IF(J6&gt;=0.6,"Profit product",IF(J6&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -757,7 +757,7 @@
         <v/>
       </c>
       <c r="N7" s="8">
-        <f>IF(A7="","",IF(K7&lt;=0,"Drop",IF(J7&gt;=0.65,"Profit product",IF(J7&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A7="","",IF(K7&lt;=0,"Drop",IF(J7&gt;=0.6,"Profit product",IF(J7&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -790,7 +790,7 @@
         <v/>
       </c>
       <c r="N8" s="8">
-        <f>IF(A8="","",IF(K8&lt;=0,"Drop",IF(J8&gt;=0.65,"Profit product",IF(J8&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A8="","",IF(K8&lt;=0,"Drop",IF(J8&gt;=0.6,"Profit product",IF(J8&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -823,7 +823,7 @@
         <v/>
       </c>
       <c r="N9" s="8">
-        <f>IF(A9="","",IF(K9&lt;=0,"Drop",IF(J9&gt;=0.65,"Profit product",IF(J9&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A9="","",IF(K9&lt;=0,"Drop",IF(J9&gt;=0.6,"Profit product",IF(J9&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -856,7 +856,7 @@
         <v/>
       </c>
       <c r="N10" s="8">
-        <f>IF(A10="","",IF(K10&lt;=0,"Drop",IF(J10&gt;=0.65,"Profit product",IF(J10&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A10="","",IF(K10&lt;=0,"Drop",IF(J10&gt;=0.6,"Profit product",IF(J10&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -889,7 +889,7 @@
         <v/>
       </c>
       <c r="N11" s="8">
-        <f>IF(A11="","",IF(K11&lt;=0,"Drop",IF(J11&gt;=0.65,"Profit product",IF(J11&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A11="","",IF(K11&lt;=0,"Drop",IF(J11&gt;=0.6,"Profit product",IF(J11&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -922,7 +922,7 @@
         <v/>
       </c>
       <c r="N12" s="8">
-        <f>IF(A12="","",IF(K12&lt;=0,"Drop",IF(J12&gt;=0.65,"Profit product",IF(J12&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A12="","",IF(K12&lt;=0,"Drop",IF(J12&gt;=0.6,"Profit product",IF(J12&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -955,7 +955,7 @@
         <v/>
       </c>
       <c r="N13" s="8">
-        <f>IF(A13="","",IF(K13&lt;=0,"Drop",IF(J13&gt;=0.65,"Profit product",IF(J13&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A13="","",IF(K13&lt;=0,"Drop",IF(J13&gt;=0.6,"Profit product",IF(J13&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -988,7 +988,7 @@
         <v/>
       </c>
       <c r="N14" s="8">
-        <f>IF(A14="","",IF(K14&lt;=0,"Drop",IF(J14&gt;=0.65,"Profit product",IF(J14&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A14="","",IF(K14&lt;=0,"Drop",IF(J14&gt;=0.6,"Profit product",IF(J14&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="N15" s="8">
-        <f>IF(A15="","",IF(K15&lt;=0,"Drop",IF(J15&gt;=0.65,"Profit product",IF(J15&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A15="","",IF(K15&lt;=0,"Drop",IF(J15&gt;=0.6,"Profit product",IF(J15&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
         <v/>
       </c>
       <c r="N16" s="8">
-        <f>IF(A16="","",IF(K16&lt;=0,"Drop",IF(J16&gt;=0.65,"Profit product",IF(J16&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A16="","",IF(K16&lt;=0,"Drop",IF(J16&gt;=0.6,"Profit product",IF(J16&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
         <v/>
       </c>
       <c r="N17" s="8">
-        <f>IF(A17="","",IF(K17&lt;=0,"Drop",IF(J17&gt;=0.65,"Profit product",IF(J17&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A17="","",IF(K17&lt;=0,"Drop",IF(J17&gt;=0.6,"Profit product",IF(J17&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         <v/>
       </c>
       <c r="N18" s="8">
-        <f>IF(A18="","",IF(K18&lt;=0,"Drop",IF(J18&gt;=0.65,"Profit product",IF(J18&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A18="","",IF(K18&lt;=0,"Drop",IF(J18&gt;=0.6,"Profit product",IF(J18&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
         <v/>
       </c>
       <c r="N19" s="8">
-        <f>IF(A19="","",IF(K19&lt;=0,"Drop",IF(J19&gt;=0.65,"Profit product",IF(J19&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A19="","",IF(K19&lt;=0,"Drop",IF(J19&gt;=0.6,"Profit product",IF(J19&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
         <v/>
       </c>
       <c r="N20" s="8">
-        <f>IF(A20="","",IF(K20&lt;=0,"Drop",IF(J20&gt;=0.65,"Profit product",IF(J20&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A20="","",IF(K20&lt;=0,"Drop",IF(J20&gt;=0.6,"Profit product",IF(J20&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
         <v/>
       </c>
       <c r="N21" s="8">
-        <f>IF(A21="","",IF(K21&lt;=0,"Drop",IF(J21&gt;=0.65,"Profit product",IF(J21&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A21="","",IF(K21&lt;=0,"Drop",IF(J21&gt;=0.6,"Profit product",IF(J21&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
         <v/>
       </c>
       <c r="N22" s="8">
-        <f>IF(A22="","",IF(K22&lt;=0,"Drop",IF(J22&gt;=0.65,"Profit product",IF(J22&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A22="","",IF(K22&lt;=0,"Drop",IF(J22&gt;=0.6,"Profit product",IF(J22&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
         <v/>
       </c>
       <c r="N23" s="8">
-        <f>IF(A23="","",IF(K23&lt;=0,"Drop",IF(J23&gt;=0.65,"Profit product",IF(J23&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A23="","",IF(K23&lt;=0,"Drop",IF(J23&gt;=0.6,"Profit product",IF(J23&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
         <v/>
       </c>
       <c r="N24" s="8">
-        <f>IF(A24="","",IF(K24&lt;=0,"Drop",IF(J24&gt;=0.65,"Profit product",IF(J24&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A24="","",IF(K24&lt;=0,"Drop",IF(J24&gt;=0.6,"Profit product",IF(J24&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v/>
       </c>
       <c r="N25" s="8">
-        <f>IF(A25="","",IF(K25&lt;=0,"Drop",IF(J25&gt;=0.65,"Profit product",IF(J25&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A25="","",IF(K25&lt;=0,"Drop",IF(J25&gt;=0.6,"Profit product",IF(J25&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
         <v/>
       </c>
       <c r="N26" s="8">
-        <f>IF(A26="","",IF(K26&lt;=0,"Drop",IF(J26&gt;=0.65,"Profit product",IF(J26&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A26="","",IF(K26&lt;=0,"Drop",IF(J26&gt;=0.6,"Profit product",IF(J26&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
         <v/>
       </c>
       <c r="N27" s="8">
-        <f>IF(A27="","",IF(K27&lt;=0,"Drop",IF(J27&gt;=0.65,"Profit product",IF(J27&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A27="","",IF(K27&lt;=0,"Drop",IF(J27&gt;=0.6,"Profit product",IF(J27&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
         <v/>
       </c>
       <c r="N28" s="8">
-        <f>IF(A28="","",IF(K28&lt;=0,"Drop",IF(J28&gt;=0.65,"Profit product",IF(J28&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A28="","",IF(K28&lt;=0,"Drop",IF(J28&gt;=0.6,"Profit product",IF(J28&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
         <v/>
       </c>
       <c r="N29" s="8">
-        <f>IF(A29="","",IF(K29&lt;=0,"Drop",IF(J29&gt;=0.65,"Profit product",IF(J29&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A29="","",IF(K29&lt;=0,"Drop",IF(J29&gt;=0.6,"Profit product",IF(J29&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
         <v/>
       </c>
       <c r="N30" s="8">
-        <f>IF(A30="","",IF(K30&lt;=0,"Drop",IF(J30&gt;=0.65,"Profit product",IF(J30&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A30="","",IF(K30&lt;=0,"Drop",IF(J30&gt;=0.6,"Profit product",IF(J30&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
         <v/>
       </c>
       <c r="N31" s="8">
-        <f>IF(A31="","",IF(K31&lt;=0,"Drop",IF(J31&gt;=0.65,"Profit product",IF(J31&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A31="","",IF(K31&lt;=0,"Drop",IF(J31&gt;=0.6,"Profit product",IF(J31&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
         <v/>
       </c>
       <c r="N32" s="8">
-        <f>IF(A32="","",IF(K32&lt;=0,"Drop",IF(J32&gt;=0.65,"Profit product",IF(J32&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A32="","",IF(K32&lt;=0,"Drop",IF(J32&gt;=0.6,"Profit product",IF(J32&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1615,7 +1615,7 @@
         <v/>
       </c>
       <c r="N33" s="8">
-        <f>IF(A33="","",IF(K33&lt;=0,"Drop",IF(J33&gt;=0.65,"Profit product",IF(J33&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A33="","",IF(K33&lt;=0,"Drop",IF(J33&gt;=0.6,"Profit product",IF(J33&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
         <v/>
       </c>
       <c r="N34" s="8">
-        <f>IF(A34="","",IF(K34&lt;=0,"Drop",IF(J34&gt;=0.65,"Profit product",IF(J34&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A34="","",IF(K34&lt;=0,"Drop",IF(J34&gt;=0.6,"Profit product",IF(J34&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
         <v/>
       </c>
       <c r="N35" s="8">
-        <f>IF(A35="","",IF(K35&lt;=0,"Drop",IF(J35&gt;=0.65,"Profit product",IF(J35&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A35="","",IF(K35&lt;=0,"Drop",IF(J35&gt;=0.6,"Profit product",IF(J35&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
         <v/>
       </c>
       <c r="N36" s="8">
-        <f>IF(A36="","",IF(K36&lt;=0,"Drop",IF(J36&gt;=0.65,"Profit product",IF(J36&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A36="","",IF(K36&lt;=0,"Drop",IF(J36&gt;=0.6,"Profit product",IF(J36&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1747,7 +1747,7 @@
         <v/>
       </c>
       <c r="N37" s="8">
-        <f>IF(A37="","",IF(K37&lt;=0,"Drop",IF(J37&gt;=0.65,"Profit product",IF(J37&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A37="","",IF(K37&lt;=0,"Drop",IF(J37&gt;=0.6,"Profit product",IF(J37&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v/>
       </c>
       <c r="N38" s="8">
-        <f>IF(A38="","",IF(K38&lt;=0,"Drop",IF(J38&gt;=0.65,"Profit product",IF(J38&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A38="","",IF(K38&lt;=0,"Drop",IF(J38&gt;=0.6,"Profit product",IF(J38&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
         <v/>
       </c>
       <c r="N39" s="8">
-        <f>IF(A39="","",IF(K39&lt;=0,"Drop",IF(J39&gt;=0.65,"Profit product",IF(J39&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A39="","",IF(K39&lt;=0,"Drop",IF(J39&gt;=0.6,"Profit product",IF(J39&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
         <v/>
       </c>
       <c r="N40" s="8">
-        <f>IF(A40="","",IF(K40&lt;=0,"Drop",IF(J40&gt;=0.65,"Profit product",IF(J40&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A40="","",IF(K40&lt;=0,"Drop",IF(J40&gt;=0.6,"Profit product",IF(J40&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v/>
       </c>
       <c r="N41" s="8">
-        <f>IF(A41="","",IF(K41&lt;=0,"Drop",IF(J41&gt;=0.65,"Profit product",IF(J41&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A41="","",IF(K41&lt;=0,"Drop",IF(J41&gt;=0.6,"Profit product",IF(J41&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
         <v/>
       </c>
       <c r="N42" s="8">
-        <f>IF(A42="","",IF(K42&lt;=0,"Drop",IF(J42&gt;=0.65,"Profit product",IF(J42&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A42="","",IF(K42&lt;=0,"Drop",IF(J42&gt;=0.6,"Profit product",IF(J42&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
         <v/>
       </c>
       <c r="N43" s="8">
-        <f>IF(A43="","",IF(K43&lt;=0,"Drop",IF(J43&gt;=0.65,"Profit product",IF(J43&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A43="","",IF(K43&lt;=0,"Drop",IF(J43&gt;=0.6,"Profit product",IF(J43&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
         <v/>
       </c>
       <c r="N44" s="8">
-        <f>IF(A44="","",IF(K44&lt;=0,"Drop",IF(J44&gt;=0.65,"Profit product",IF(J44&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A44="","",IF(K44&lt;=0,"Drop",IF(J44&gt;=0.6,"Profit product",IF(J44&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
         <v/>
       </c>
       <c r="N45" s="8">
-        <f>IF(A45="","",IF(K45&lt;=0,"Drop",IF(J45&gt;=0.65,"Profit product",IF(J45&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A45="","",IF(K45&lt;=0,"Drop",IF(J45&gt;=0.6,"Profit product",IF(J45&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
         <v/>
       </c>
       <c r="N46" s="8">
-        <f>IF(A46="","",IF(K46&lt;=0,"Drop",IF(J46&gt;=0.65,"Profit product",IF(J46&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A46="","",IF(K46&lt;=0,"Drop",IF(J46&gt;=0.6,"Profit product",IF(J46&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
         <v/>
       </c>
       <c r="N47" s="8">
-        <f>IF(A47="","",IF(K47&lt;=0,"Drop",IF(J47&gt;=0.65,"Profit product",IF(J47&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A47="","",IF(K47&lt;=0,"Drop",IF(J47&gt;=0.6,"Profit product",IF(J47&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
         <v/>
       </c>
       <c r="N48" s="8">
-        <f>IF(A48="","",IF(K48&lt;=0,"Drop",IF(J48&gt;=0.65,"Profit product",IF(J48&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A48="","",IF(K48&lt;=0,"Drop",IF(J48&gt;=0.6,"Profit product",IF(J48&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
         <v/>
       </c>
       <c r="N49" s="8">
-        <f>IF(A49="","",IF(K49&lt;=0,"Drop",IF(J49&gt;=0.65,"Profit product",IF(J49&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A49="","",IF(K49&lt;=0,"Drop",IF(J49&gt;=0.6,"Profit product",IF(J49&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
         <v/>
       </c>
       <c r="N50" s="8">
-        <f>IF(A50="","",IF(K50&lt;=0,"Drop",IF(J50&gt;=0.65,"Profit product",IF(J50&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A50="","",IF(K50&lt;=0,"Drop",IF(J50&gt;=0.6,"Profit product",IF(J50&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
         <v/>
       </c>
       <c r="N51" s="8">
-        <f>IF(A51="","",IF(K51&lt;=0,"Drop",IF(J51&gt;=0.65,"Profit product",IF(J51&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A51="","",IF(K51&lt;=0,"Drop",IF(J51&gt;=0.6,"Profit product",IF(J51&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
         <v/>
       </c>
       <c r="N52" s="8">
-        <f>IF(A52="","",IF(K52&lt;=0,"Drop",IF(J52&gt;=0.65,"Profit product",IF(J52&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A52="","",IF(K52&lt;=0,"Drop",IF(J52&gt;=0.6,"Profit product",IF(J52&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="N53" s="8">
-        <f>IF(A53="","",IF(K53&lt;=0,"Drop",IF(J53&gt;=0.65,"Profit product",IF(J53&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A53="","",IF(K53&lt;=0,"Drop",IF(J53&gt;=0.6,"Profit product",IF(J53&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
         <v/>
       </c>
       <c r="N54" s="8">
-        <f>IF(A54="","",IF(K54&lt;=0,"Drop",IF(J54&gt;=0.65,"Profit product",IF(J54&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A54="","",IF(K54&lt;=0,"Drop",IF(J54&gt;=0.6,"Profit product",IF(J54&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
         <v/>
       </c>
       <c r="N55" s="8">
-        <f>IF(A55="","",IF(K55&lt;=0,"Drop",IF(J55&gt;=0.65,"Profit product",IF(J55&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A55="","",IF(K55&lt;=0,"Drop",IF(J55&gt;=0.6,"Profit product",IF(J55&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
         <v/>
       </c>
       <c r="N56" s="8">
-        <f>IF(A56="","",IF(K56&lt;=0,"Drop",IF(J56&gt;=0.65,"Profit product",IF(J56&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A56="","",IF(K56&lt;=0,"Drop",IF(J56&gt;=0.6,"Profit product",IF(J56&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
         <v/>
       </c>
       <c r="N57" s="8">
-        <f>IF(A57="","",IF(K57&lt;=0,"Drop",IF(J57&gt;=0.65,"Profit product",IF(J57&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A57="","",IF(K57&lt;=0,"Drop",IF(J57&gt;=0.6,"Profit product",IF(J57&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
         <v/>
       </c>
       <c r="N58" s="8">
-        <f>IF(A58="","",IF(K58&lt;=0,"Drop",IF(J58&gt;=0.65,"Profit product",IF(J58&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A58="","",IF(K58&lt;=0,"Drop",IF(J58&gt;=0.6,"Profit product",IF(J58&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
         <v/>
       </c>
       <c r="N59" s="8">
-        <f>IF(A59="","",IF(K59&lt;=0,"Drop",IF(J59&gt;=0.65,"Profit product",IF(J59&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A59="","",IF(K59&lt;=0,"Drop",IF(J59&gt;=0.6,"Profit product",IF(J59&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v/>
       </c>
       <c r="N60" s="8">
-        <f>IF(A60="","",IF(K60&lt;=0,"Drop",IF(J60&gt;=0.65,"Profit product",IF(J60&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A60="","",IF(K60&lt;=0,"Drop",IF(J60&gt;=0.6,"Profit product",IF(J60&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2539,7 +2539,7 @@
         <v/>
       </c>
       <c r="N61" s="8">
-        <f>IF(A61="","",IF(K61&lt;=0,"Drop",IF(J61&gt;=0.65,"Profit product",IF(J61&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A61="","",IF(K61&lt;=0,"Drop",IF(J61&gt;=0.6,"Profit product",IF(J61&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
         <v/>
       </c>
       <c r="N62" s="8">
-        <f>IF(A62="","",IF(K62&lt;=0,"Drop",IF(J62&gt;=0.65,"Profit product",IF(J62&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A62="","",IF(K62&lt;=0,"Drop",IF(J62&gt;=0.6,"Profit product",IF(J62&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="N63" s="8">
-        <f>IF(A63="","",IF(K63&lt;=0,"Drop",IF(J63&gt;=0.65,"Profit product",IF(J63&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A63="","",IF(K63&lt;=0,"Drop",IF(J63&gt;=0.6,"Profit product",IF(J63&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v/>
       </c>
       <c r="N64" s="8">
-        <f>IF(A64="","",IF(K64&lt;=0,"Drop",IF(J64&gt;=0.65,"Profit product",IF(J64&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A64="","",IF(K64&lt;=0,"Drop",IF(J64&gt;=0.6,"Profit product",IF(J64&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
         <v/>
       </c>
       <c r="N65" s="8">
-        <f>IF(A65="","",IF(K65&lt;=0,"Drop",IF(J65&gt;=0.65,"Profit product",IF(J65&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A65="","",IF(K65&lt;=0,"Drop",IF(J65&gt;=0.6,"Profit product",IF(J65&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
         <v/>
       </c>
       <c r="N66" s="8">
-        <f>IF(A66="","",IF(K66&lt;=0,"Drop",IF(J66&gt;=0.65,"Profit product",IF(J66&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A66="","",IF(K66&lt;=0,"Drop",IF(J66&gt;=0.6,"Profit product",IF(J66&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="N67" s="8">
-        <f>IF(A67="","",IF(K67&lt;=0,"Drop",IF(J67&gt;=0.65,"Profit product",IF(J67&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A67="","",IF(K67&lt;=0,"Drop",IF(J67&gt;=0.6,"Profit product",IF(J67&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2770,7 +2770,7 @@
         <v/>
       </c>
       <c r="N68" s="8">
-        <f>IF(A68="","",IF(K68&lt;=0,"Drop",IF(J68&gt;=0.65,"Profit product",IF(J68&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A68="","",IF(K68&lt;=0,"Drop",IF(J68&gt;=0.6,"Profit product",IF(J68&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
         <v/>
       </c>
       <c r="N69" s="8">
-        <f>IF(A69="","",IF(K69&lt;=0,"Drop",IF(J69&gt;=0.65,"Profit product",IF(J69&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A69="","",IF(K69&lt;=0,"Drop",IF(J69&gt;=0.6,"Profit product",IF(J69&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
         <v/>
       </c>
       <c r="N70" s="8">
-        <f>IF(A70="","",IF(K70&lt;=0,"Drop",IF(J70&gt;=0.65,"Profit product",IF(J70&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A70="","",IF(K70&lt;=0,"Drop",IF(J70&gt;=0.6,"Profit product",IF(J70&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2869,7 +2869,7 @@
         <v/>
       </c>
       <c r="N71" s="8">
-        <f>IF(A71="","",IF(K71&lt;=0,"Drop",IF(J71&gt;=0.65,"Profit product",IF(J71&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A71="","",IF(K71&lt;=0,"Drop",IF(J71&gt;=0.6,"Profit product",IF(J71&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
         <v/>
       </c>
       <c r="N72" s="8">
-        <f>IF(A72="","",IF(K72&lt;=0,"Drop",IF(J72&gt;=0.65,"Profit product",IF(J72&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A72="","",IF(K72&lt;=0,"Drop",IF(J72&gt;=0.6,"Profit product",IF(J72&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2935,7 +2935,7 @@
         <v/>
       </c>
       <c r="N73" s="8">
-        <f>IF(A73="","",IF(K73&lt;=0,"Drop",IF(J73&gt;=0.65,"Profit product",IF(J73&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A73="","",IF(K73&lt;=0,"Drop",IF(J73&gt;=0.6,"Profit product",IF(J73&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
         <v/>
       </c>
       <c r="N74" s="8">
-        <f>IF(A74="","",IF(K74&lt;=0,"Drop",IF(J74&gt;=0.65,"Profit product",IF(J74&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A74="","",IF(K74&lt;=0,"Drop",IF(J74&gt;=0.6,"Profit product",IF(J74&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
         <v/>
       </c>
       <c r="N75" s="8">
-        <f>IF(A75="","",IF(K75&lt;=0,"Drop",IF(J75&gt;=0.65,"Profit product",IF(J75&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A75="","",IF(K75&lt;=0,"Drop",IF(J75&gt;=0.6,"Profit product",IF(J75&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
         <v/>
       </c>
       <c r="N76" s="8">
-        <f>IF(A76="","",IF(K76&lt;=0,"Drop",IF(J76&gt;=0.65,"Profit product",IF(J76&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A76="","",IF(K76&lt;=0,"Drop",IF(J76&gt;=0.6,"Profit product",IF(J76&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         <v/>
       </c>
       <c r="N77" s="8">
-        <f>IF(A77="","",IF(K77&lt;=0,"Drop",IF(J77&gt;=0.65,"Profit product",IF(J77&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A77="","",IF(K77&lt;=0,"Drop",IF(J77&gt;=0.6,"Profit product",IF(J77&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
         <v/>
       </c>
       <c r="N78" s="8">
-        <f>IF(A78="","",IF(K78&lt;=0,"Drop",IF(J78&gt;=0.65,"Profit product",IF(J78&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A78="","",IF(K78&lt;=0,"Drop",IF(J78&gt;=0.6,"Profit product",IF(J78&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
         <v/>
       </c>
       <c r="N79" s="8">
-        <f>IF(A79="","",IF(K79&lt;=0,"Drop",IF(J79&gt;=0.65,"Profit product",IF(J79&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A79="","",IF(K79&lt;=0,"Drop",IF(J79&gt;=0.6,"Profit product",IF(J79&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
         <v/>
       </c>
       <c r="N80" s="8">
-        <f>IF(A80="","",IF(K80&lt;=0,"Drop",IF(J80&gt;=0.65,"Profit product",IF(J80&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A80="","",IF(K80&lt;=0,"Drop",IF(J80&gt;=0.6,"Profit product",IF(J80&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
         <v/>
       </c>
       <c r="N81" s="8">
-        <f>IF(A81="","",IF(K81&lt;=0,"Drop",IF(J81&gt;=0.65,"Profit product",IF(J81&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A81="","",IF(K81&lt;=0,"Drop",IF(J81&gt;=0.6,"Profit product",IF(J81&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
         <v/>
       </c>
       <c r="N82" s="8">
-        <f>IF(A82="","",IF(K82&lt;=0,"Drop",IF(J82&gt;=0.65,"Profit product",IF(J82&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A82="","",IF(K82&lt;=0,"Drop",IF(J82&gt;=0.6,"Profit product",IF(J82&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
         <v/>
       </c>
       <c r="N83" s="8">
-        <f>IF(A83="","",IF(K83&lt;=0,"Drop",IF(J83&gt;=0.65,"Profit product",IF(J83&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A83="","",IF(K83&lt;=0,"Drop",IF(J83&gt;=0.6,"Profit product",IF(J83&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
         <v/>
       </c>
       <c r="N84" s="8">
-        <f>IF(A84="","",IF(K84&lt;=0,"Drop",IF(J84&gt;=0.65,"Profit product",IF(J84&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A84="","",IF(K84&lt;=0,"Drop",IF(J84&gt;=0.6,"Profit product",IF(J84&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
         <v/>
       </c>
       <c r="N85" s="8">
-        <f>IF(A85="","",IF(K85&lt;=0,"Drop",IF(J85&gt;=0.65,"Profit product",IF(J85&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A85="","",IF(K85&lt;=0,"Drop",IF(J85&gt;=0.6,"Profit product",IF(J85&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
         <v/>
       </c>
       <c r="N86" s="8">
-        <f>IF(A86="","",IF(K86&lt;=0,"Drop",IF(J86&gt;=0.65,"Profit product",IF(J86&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A86="","",IF(K86&lt;=0,"Drop",IF(J86&gt;=0.6,"Profit product",IF(J86&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         <v/>
       </c>
       <c r="N87" s="8">
-        <f>IF(A87="","",IF(K87&lt;=0,"Drop",IF(J87&gt;=0.65,"Profit product",IF(J87&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A87="","",IF(K87&lt;=0,"Drop",IF(J87&gt;=0.6,"Profit product",IF(J87&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
         <v/>
       </c>
       <c r="N88" s="8">
-        <f>IF(A88="","",IF(K88&lt;=0,"Drop",IF(J88&gt;=0.65,"Profit product",IF(J88&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A88="","",IF(K88&lt;=0,"Drop",IF(J88&gt;=0.6,"Profit product",IF(J88&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
         <v/>
       </c>
       <c r="N89" s="8">
-        <f>IF(A89="","",IF(K89&lt;=0,"Drop",IF(J89&gt;=0.65,"Profit product",IF(J89&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A89="","",IF(K89&lt;=0,"Drop",IF(J89&gt;=0.6,"Profit product",IF(J89&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
         <v/>
       </c>
       <c r="N90" s="8">
-        <f>IF(A90="","",IF(K90&lt;=0,"Drop",IF(J90&gt;=0.65,"Profit product",IF(J90&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A90="","",IF(K90&lt;=0,"Drop",IF(J90&gt;=0.6,"Profit product",IF(J90&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="N91" s="8">
-        <f>IF(A91="","",IF(K91&lt;=0,"Drop",IF(J91&gt;=0.65,"Profit product",IF(J91&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A91="","",IF(K91&lt;=0,"Drop",IF(J91&gt;=0.6,"Profit product",IF(J91&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3562,7 +3562,7 @@
         <v/>
       </c>
       <c r="N92" s="8">
-        <f>IF(A92="","",IF(K92&lt;=0,"Drop",IF(J92&gt;=0.65,"Profit product",IF(J92&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A92="","",IF(K92&lt;=0,"Drop",IF(J92&gt;=0.6,"Profit product",IF(J92&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3595,7 +3595,7 @@
         <v/>
       </c>
       <c r="N93" s="8">
-        <f>IF(A93="","",IF(K93&lt;=0,"Drop",IF(J93&gt;=0.65,"Profit product",IF(J93&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A93="","",IF(K93&lt;=0,"Drop",IF(J93&gt;=0.6,"Profit product",IF(J93&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
         <v/>
       </c>
       <c r="N94" s="8">
-        <f>IF(A94="","",IF(K94&lt;=0,"Drop",IF(J94&gt;=0.65,"Profit product",IF(J94&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A94="","",IF(K94&lt;=0,"Drop",IF(J94&gt;=0.6,"Profit product",IF(J94&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
         <v/>
       </c>
       <c r="N95" s="8">
-        <f>IF(A95="","",IF(K95&lt;=0,"Drop",IF(J95&gt;=0.65,"Profit product",IF(J95&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A95="","",IF(K95&lt;=0,"Drop",IF(J95&gt;=0.6,"Profit product",IF(J95&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
         <v/>
       </c>
       <c r="N96" s="8">
-        <f>IF(A96="","",IF(K96&lt;=0,"Drop",IF(J96&gt;=0.65,"Profit product",IF(J96&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A96="","",IF(K96&lt;=0,"Drop",IF(J96&gt;=0.6,"Profit product",IF(J96&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
         <v/>
       </c>
       <c r="N97" s="8">
-        <f>IF(A97="","",IF(K97&lt;=0,"Drop",IF(J97&gt;=0.65,"Profit product",IF(J97&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A97="","",IF(K97&lt;=0,"Drop",IF(J97&gt;=0.6,"Profit product",IF(J97&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
         <v/>
       </c>
       <c r="N98" s="8">
-        <f>IF(A98="","",IF(K98&lt;=0,"Drop",IF(J98&gt;=0.65,"Profit product",IF(J98&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A98="","",IF(K98&lt;=0,"Drop",IF(J98&gt;=0.6,"Profit product",IF(J98&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3793,7 +3793,7 @@
         <v/>
       </c>
       <c r="N99" s="8">
-        <f>IF(A99="","",IF(K99&lt;=0,"Drop",IF(J99&gt;=0.65,"Profit product",IF(J99&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A99="","",IF(K99&lt;=0,"Drop",IF(J99&gt;=0.6,"Profit product",IF(J99&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3826,7 +3826,7 @@
         <v/>
       </c>
       <c r="N100" s="8">
-        <f>IF(A100="","",IF(K100&lt;=0,"Drop",IF(J100&gt;=0.65,"Profit product",IF(J100&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A100="","",IF(K100&lt;=0,"Drop",IF(J100&gt;=0.6,"Profit product",IF(J100&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
         <v/>
       </c>
       <c r="N101" s="8">
-        <f>IF(A101="","",IF(K101&lt;=0,"Drop",IF(J101&gt;=0.65,"Profit product",IF(J101&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A101="","",IF(K101&lt;=0,"Drop",IF(J101&gt;=0.6,"Profit product",IF(J101&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
         <v/>
       </c>
       <c r="N102" s="8">
-        <f>IF(A102="","",IF(K102&lt;=0,"Drop",IF(J102&gt;=0.65,"Profit product",IF(J102&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A102="","",IF(K102&lt;=0,"Drop",IF(J102&gt;=0.6,"Profit product",IF(J102&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
         <v/>
       </c>
       <c r="N103" s="8">
-        <f>IF(A103="","",IF(K103&lt;=0,"Drop",IF(J103&gt;=0.65,"Profit product",IF(J103&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A103="","",IF(K103&lt;=0,"Drop",IF(J103&gt;=0.6,"Profit product",IF(J103&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
         <v/>
       </c>
       <c r="N104" s="8">
-        <f>IF(A104="","",IF(K104&lt;=0,"Drop",IF(J104&gt;=0.65,"Profit product",IF(J104&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A104="","",IF(K104&lt;=0,"Drop",IF(J104&gt;=0.6,"Profit product",IF(J104&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="N105" s="8">
-        <f>IF(A105="","",IF(K105&lt;=0,"Drop",IF(J105&gt;=0.65,"Profit product",IF(J105&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A105="","",IF(K105&lt;=0,"Drop",IF(J105&gt;=0.6,"Profit product",IF(J105&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
         <v/>
       </c>
       <c r="N106" s="8">
-        <f>IF(A106="","",IF(K106&lt;=0,"Drop",IF(J106&gt;=0.65,"Profit product",IF(J106&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A106="","",IF(K106&lt;=0,"Drop",IF(J106&gt;=0.6,"Profit product",IF(J106&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4057,7 +4057,7 @@
         <v/>
       </c>
       <c r="N107" s="8">
-        <f>IF(A107="","",IF(K107&lt;=0,"Drop",IF(J107&gt;=0.65,"Profit product",IF(J107&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A107="","",IF(K107&lt;=0,"Drop",IF(J107&gt;=0.6,"Profit product",IF(J107&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
         <v/>
       </c>
       <c r="N108" s="8">
-        <f>IF(A108="","",IF(K108&lt;=0,"Drop",IF(J108&gt;=0.65,"Profit product",IF(J108&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A108="","",IF(K108&lt;=0,"Drop",IF(J108&gt;=0.6,"Profit product",IF(J108&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
         <v/>
       </c>
       <c r="N109" s="8">
-        <f>IF(A109="","",IF(K109&lt;=0,"Drop",IF(J109&gt;=0.65,"Profit product",IF(J109&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A109="","",IF(K109&lt;=0,"Drop",IF(J109&gt;=0.6,"Profit product",IF(J109&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4156,7 +4156,7 @@
         <v/>
       </c>
       <c r="N110" s="8">
-        <f>IF(A110="","",IF(K110&lt;=0,"Drop",IF(J110&gt;=0.65,"Profit product",IF(J110&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A110="","",IF(K110&lt;=0,"Drop",IF(J110&gt;=0.6,"Profit product",IF(J110&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4189,7 +4189,7 @@
         <v/>
       </c>
       <c r="N111" s="8">
-        <f>IF(A111="","",IF(K111&lt;=0,"Drop",IF(J111&gt;=0.65,"Profit product",IF(J111&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A111="","",IF(K111&lt;=0,"Drop",IF(J111&gt;=0.6,"Profit product",IF(J111&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
         <v/>
       </c>
       <c r="N112" s="8">
-        <f>IF(A112="","",IF(K112&lt;=0,"Drop",IF(J112&gt;=0.65,"Profit product",IF(J112&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A112="","",IF(K112&lt;=0,"Drop",IF(J112&gt;=0.6,"Profit product",IF(J112&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         <v/>
       </c>
       <c r="N113" s="8">
-        <f>IF(A113="","",IF(K113&lt;=0,"Drop",IF(J113&gt;=0.65,"Profit product",IF(J113&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A113="","",IF(K113&lt;=0,"Drop",IF(J113&gt;=0.6,"Profit product",IF(J113&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
         <v/>
       </c>
       <c r="N114" s="8">
-        <f>IF(A114="","",IF(K114&lt;=0,"Drop",IF(J114&gt;=0.65,"Profit product",IF(J114&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A114="","",IF(K114&lt;=0,"Drop",IF(J114&gt;=0.6,"Profit product",IF(J114&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4321,7 +4321,7 @@
         <v/>
       </c>
       <c r="N115" s="8">
-        <f>IF(A115="","",IF(K115&lt;=0,"Drop",IF(J115&gt;=0.65,"Profit product",IF(J115&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A115="","",IF(K115&lt;=0,"Drop",IF(J115&gt;=0.6,"Profit product",IF(J115&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
         <v/>
       </c>
       <c r="N116" s="8">
-        <f>IF(A116="","",IF(K116&lt;=0,"Drop",IF(J116&gt;=0.65,"Profit product",IF(J116&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A116="","",IF(K116&lt;=0,"Drop",IF(J116&gt;=0.6,"Profit product",IF(J116&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4387,7 +4387,7 @@
         <v/>
       </c>
       <c r="N117" s="8">
-        <f>IF(A117="","",IF(K117&lt;=0,"Drop",IF(J117&gt;=0.65,"Profit product",IF(J117&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A117="","",IF(K117&lt;=0,"Drop",IF(J117&gt;=0.6,"Profit product",IF(J117&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
         <v/>
       </c>
       <c r="N118" s="8">
-        <f>IF(A118="","",IF(K118&lt;=0,"Drop",IF(J118&gt;=0.65,"Profit product",IF(J118&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A118="","",IF(K118&lt;=0,"Drop",IF(J118&gt;=0.6,"Profit product",IF(J118&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
         <v/>
       </c>
       <c r="N119" s="8">
-        <f>IF(A119="","",IF(K119&lt;=0,"Drop",IF(J119&gt;=0.65,"Profit product",IF(J119&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A119="","",IF(K119&lt;=0,"Drop",IF(J119&gt;=0.6,"Profit product",IF(J119&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
         <v/>
       </c>
       <c r="N120" s="8">
-        <f>IF(A120="","",IF(K120&lt;=0,"Drop",IF(J120&gt;=0.65,"Profit product",IF(J120&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A120="","",IF(K120&lt;=0,"Drop",IF(J120&gt;=0.6,"Profit product",IF(J120&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
         <v/>
       </c>
       <c r="N121" s="8">
-        <f>IF(A121="","",IF(K121&lt;=0,"Drop",IF(J121&gt;=0.65,"Profit product",IF(J121&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A121="","",IF(K121&lt;=0,"Drop",IF(J121&gt;=0.6,"Profit product",IF(J121&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
         <v/>
       </c>
       <c r="N122" s="8">
-        <f>IF(A122="","",IF(K122&lt;=0,"Drop",IF(J122&gt;=0.65,"Profit product",IF(J122&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A122="","",IF(K122&lt;=0,"Drop",IF(J122&gt;=0.6,"Profit product",IF(J122&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
         <v/>
       </c>
       <c r="N123" s="8">
-        <f>IF(A123="","",IF(K123&lt;=0,"Drop",IF(J123&gt;=0.65,"Profit product",IF(J123&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A123="","",IF(K123&lt;=0,"Drop",IF(J123&gt;=0.6,"Profit product",IF(J123&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
         <v/>
       </c>
       <c r="N124" s="8">
-        <f>IF(A124="","",IF(K124&lt;=0,"Drop",IF(J124&gt;=0.65,"Profit product",IF(J124&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A124="","",IF(K124&lt;=0,"Drop",IF(J124&gt;=0.6,"Profit product",IF(J124&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
         <v/>
       </c>
       <c r="N125" s="8">
-        <f>IF(A125="","",IF(K125&lt;=0,"Drop",IF(J125&gt;=0.65,"Profit product",IF(J125&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A125="","",IF(K125&lt;=0,"Drop",IF(J125&gt;=0.6,"Profit product",IF(J125&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
         <v/>
       </c>
       <c r="N126" s="8">
-        <f>IF(A126="","",IF(K126&lt;=0,"Drop",IF(J126&gt;=0.65,"Profit product",IF(J126&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A126="","",IF(K126&lt;=0,"Drop",IF(J126&gt;=0.6,"Profit product",IF(J126&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
         <v/>
       </c>
       <c r="N127" s="8">
-        <f>IF(A127="","",IF(K127&lt;=0,"Drop",IF(J127&gt;=0.65,"Profit product",IF(J127&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A127="","",IF(K127&lt;=0,"Drop",IF(J127&gt;=0.6,"Profit product",IF(J127&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
         <v/>
       </c>
       <c r="N128" s="8">
-        <f>IF(A128="","",IF(K128&lt;=0,"Drop",IF(J128&gt;=0.65,"Profit product",IF(J128&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A128="","",IF(K128&lt;=0,"Drop",IF(J128&gt;=0.6,"Profit product",IF(J128&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
         <v/>
       </c>
       <c r="N129" s="8">
-        <f>IF(A129="","",IF(K129&lt;=0,"Drop",IF(J129&gt;=0.65,"Profit product",IF(J129&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A129="","",IF(K129&lt;=0,"Drop",IF(J129&gt;=0.6,"Profit product",IF(J129&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
         <v/>
       </c>
       <c r="N130" s="8">
-        <f>IF(A130="","",IF(K130&lt;=0,"Drop",IF(J130&gt;=0.65,"Profit product",IF(J130&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A130="","",IF(K130&lt;=0,"Drop",IF(J130&gt;=0.6,"Profit product",IF(J130&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
         <v/>
       </c>
       <c r="N131" s="8">
-        <f>IF(A131="","",IF(K131&lt;=0,"Drop",IF(J131&gt;=0.65,"Profit product",IF(J131&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A131="","",IF(K131&lt;=0,"Drop",IF(J131&gt;=0.6,"Profit product",IF(J131&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
         <v/>
       </c>
       <c r="N132" s="8">
-        <f>IF(A132="","",IF(K132&lt;=0,"Drop",IF(J132&gt;=0.65,"Profit product",IF(J132&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A132="","",IF(K132&lt;=0,"Drop",IF(J132&gt;=0.6,"Profit product",IF(J132&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4915,7 +4915,7 @@
         <v/>
       </c>
       <c r="N133" s="8">
-        <f>IF(A133="","",IF(K133&lt;=0,"Drop",IF(J133&gt;=0.65,"Profit product",IF(J133&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A133="","",IF(K133&lt;=0,"Drop",IF(J133&gt;=0.6,"Profit product",IF(J133&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
         <v/>
       </c>
       <c r="N134" s="8">
-        <f>IF(A134="","",IF(K134&lt;=0,"Drop",IF(J134&gt;=0.65,"Profit product",IF(J134&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A134="","",IF(K134&lt;=0,"Drop",IF(J134&gt;=0.6,"Profit product",IF(J134&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
         <v/>
       </c>
       <c r="N135" s="8">
-        <f>IF(A135="","",IF(K135&lt;=0,"Drop",IF(J135&gt;=0.65,"Profit product",IF(J135&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A135="","",IF(K135&lt;=0,"Drop",IF(J135&gt;=0.6,"Profit product",IF(J135&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5014,7 +5014,7 @@
         <v/>
       </c>
       <c r="N136" s="8">
-        <f>IF(A136="","",IF(K136&lt;=0,"Drop",IF(J136&gt;=0.65,"Profit product",IF(J136&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A136="","",IF(K136&lt;=0,"Drop",IF(J136&gt;=0.6,"Profit product",IF(J136&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5047,7 +5047,7 @@
         <v/>
       </c>
       <c r="N137" s="8">
-        <f>IF(A137="","",IF(K137&lt;=0,"Drop",IF(J137&gt;=0.65,"Profit product",IF(J137&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A137="","",IF(K137&lt;=0,"Drop",IF(J137&gt;=0.6,"Profit product",IF(J137&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5080,7 +5080,7 @@
         <v/>
       </c>
       <c r="N138" s="8">
-        <f>IF(A138="","",IF(K138&lt;=0,"Drop",IF(J138&gt;=0.65,"Profit product",IF(J138&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A138="","",IF(K138&lt;=0,"Drop",IF(J138&gt;=0.6,"Profit product",IF(J138&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5113,7 +5113,7 @@
         <v/>
       </c>
       <c r="N139" s="8">
-        <f>IF(A139="","",IF(K139&lt;=0,"Drop",IF(J139&gt;=0.65,"Profit product",IF(J139&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A139="","",IF(K139&lt;=0,"Drop",IF(J139&gt;=0.6,"Profit product",IF(J139&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
         <v/>
       </c>
       <c r="N140" s="8">
-        <f>IF(A140="","",IF(K140&lt;=0,"Drop",IF(J140&gt;=0.65,"Profit product",IF(J140&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A140="","",IF(K140&lt;=0,"Drop",IF(J140&gt;=0.6,"Profit product",IF(J140&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
         <v/>
       </c>
       <c r="N141" s="8">
-        <f>IF(A141="","",IF(K141&lt;=0,"Drop",IF(J141&gt;=0.65,"Profit product",IF(J141&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A141="","",IF(K141&lt;=0,"Drop",IF(J141&gt;=0.6,"Profit product",IF(J141&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5212,7 +5212,7 @@
         <v/>
       </c>
       <c r="N142" s="8">
-        <f>IF(A142="","",IF(K142&lt;=0,"Drop",IF(J142&gt;=0.65,"Profit product",IF(J142&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A142="","",IF(K142&lt;=0,"Drop",IF(J142&gt;=0.6,"Profit product",IF(J142&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5245,7 +5245,7 @@
         <v/>
       </c>
       <c r="N143" s="8">
-        <f>IF(A143="","",IF(K143&lt;=0,"Drop",IF(J143&gt;=0.65,"Profit product",IF(J143&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A143="","",IF(K143&lt;=0,"Drop",IF(J143&gt;=0.6,"Profit product",IF(J143&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
         <v/>
       </c>
       <c r="N144" s="8">
-        <f>IF(A144="","",IF(K144&lt;=0,"Drop",IF(J144&gt;=0.65,"Profit product",IF(J144&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A144="","",IF(K144&lt;=0,"Drop",IF(J144&gt;=0.6,"Profit product",IF(J144&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5311,7 +5311,7 @@
         <v/>
       </c>
       <c r="N145" s="8">
-        <f>IF(A145="","",IF(K145&lt;=0,"Drop",IF(J145&gt;=0.65,"Profit product",IF(J145&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A145="","",IF(K145&lt;=0,"Drop",IF(J145&gt;=0.6,"Profit product",IF(J145&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5344,7 +5344,7 @@
         <v/>
       </c>
       <c r="N146" s="8">
-        <f>IF(A146="","",IF(K146&lt;=0,"Drop",IF(J146&gt;=0.65,"Profit product",IF(J146&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A146="","",IF(K146&lt;=0,"Drop",IF(J146&gt;=0.6,"Profit product",IF(J146&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
         <v/>
       </c>
       <c r="N147" s="8">
-        <f>IF(A147="","",IF(K147&lt;=0,"Drop",IF(J147&gt;=0.65,"Profit product",IF(J147&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A147="","",IF(K147&lt;=0,"Drop",IF(J147&gt;=0.6,"Profit product",IF(J147&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5410,7 +5410,7 @@
         <v/>
       </c>
       <c r="N148" s="8">
-        <f>IF(A148="","",IF(K148&lt;=0,"Drop",IF(J148&gt;=0.65,"Profit product",IF(J148&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A148="","",IF(K148&lt;=0,"Drop",IF(J148&gt;=0.6,"Profit product",IF(J148&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5443,7 +5443,7 @@
         <v/>
       </c>
       <c r="N149" s="8">
-        <f>IF(A149="","",IF(K149&lt;=0,"Drop",IF(J149&gt;=0.65,"Profit product",IF(J149&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A149="","",IF(K149&lt;=0,"Drop",IF(J149&gt;=0.6,"Profit product",IF(J149&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
         <v/>
       </c>
       <c r="N150" s="8">
-        <f>IF(A150="","",IF(K150&lt;=0,"Drop",IF(J150&gt;=0.65,"Profit product",IF(J150&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A150="","",IF(K150&lt;=0,"Drop",IF(J150&gt;=0.6,"Profit product",IF(J150&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
         <v/>
       </c>
       <c r="N151" s="8">
-        <f>IF(A151="","",IF(K151&lt;=0,"Drop",IF(J151&gt;=0.65,"Profit product",IF(J151&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A151="","",IF(K151&lt;=0,"Drop",IF(J151&gt;=0.6,"Profit product",IF(J151&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
         <v/>
       </c>
       <c r="N152" s="8">
-        <f>IF(A152="","",IF(K152&lt;=0,"Drop",IF(J152&gt;=0.65,"Profit product",IF(J152&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A152="","",IF(K152&lt;=0,"Drop",IF(J152&gt;=0.6,"Profit product",IF(J152&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5575,7 +5575,7 @@
         <v/>
       </c>
       <c r="N153" s="8">
-        <f>IF(A153="","",IF(K153&lt;=0,"Drop",IF(J153&gt;=0.65,"Profit product",IF(J153&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A153="","",IF(K153&lt;=0,"Drop",IF(J153&gt;=0.6,"Profit product",IF(J153&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
         <v/>
       </c>
       <c r="N154" s="8">
-        <f>IF(A154="","",IF(K154&lt;=0,"Drop",IF(J154&gt;=0.65,"Profit product",IF(J154&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A154="","",IF(K154&lt;=0,"Drop",IF(J154&gt;=0.6,"Profit product",IF(J154&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5641,7 +5641,7 @@
         <v/>
       </c>
       <c r="N155" s="8">
-        <f>IF(A155="","",IF(K155&lt;=0,"Drop",IF(J155&gt;=0.65,"Profit product",IF(J155&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A155="","",IF(K155&lt;=0,"Drop",IF(J155&gt;=0.6,"Profit product",IF(J155&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
         <v/>
       </c>
       <c r="N156" s="8">
-        <f>IF(A156="","",IF(K156&lt;=0,"Drop",IF(J156&gt;=0.65,"Profit product",IF(J156&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A156="","",IF(K156&lt;=0,"Drop",IF(J156&gt;=0.6,"Profit product",IF(J156&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5707,7 +5707,7 @@
         <v/>
       </c>
       <c r="N157" s="8">
-        <f>IF(A157="","",IF(K157&lt;=0,"Drop",IF(J157&gt;=0.65,"Profit product",IF(J157&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A157="","",IF(K157&lt;=0,"Drop",IF(J157&gt;=0.6,"Profit product",IF(J157&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5740,7 +5740,7 @@
         <v/>
       </c>
       <c r="N158" s="8">
-        <f>IF(A158="","",IF(K158&lt;=0,"Drop",IF(J158&gt;=0.65,"Profit product",IF(J158&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A158="","",IF(K158&lt;=0,"Drop",IF(J158&gt;=0.6,"Profit product",IF(J158&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5773,7 +5773,7 @@
         <v/>
       </c>
       <c r="N159" s="8">
-        <f>IF(A159="","",IF(K159&lt;=0,"Drop",IF(J159&gt;=0.65,"Profit product",IF(J159&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A159="","",IF(K159&lt;=0,"Drop",IF(J159&gt;=0.6,"Profit product",IF(J159&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
         <v/>
       </c>
       <c r="N160" s="8">
-        <f>IF(A160="","",IF(K160&lt;=0,"Drop",IF(J160&gt;=0.65,"Profit product",IF(J160&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A160="","",IF(K160&lt;=0,"Drop",IF(J160&gt;=0.6,"Profit product",IF(J160&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
         <v/>
       </c>
       <c r="N161" s="8">
-        <f>IF(A161="","",IF(K161&lt;=0,"Drop",IF(J161&gt;=0.65,"Profit product",IF(J161&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A161="","",IF(K161&lt;=0,"Drop",IF(J161&gt;=0.6,"Profit product",IF(J161&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
         <v/>
       </c>
       <c r="N162" s="8">
-        <f>IF(A162="","",IF(K162&lt;=0,"Drop",IF(J162&gt;=0.65,"Profit product",IF(J162&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A162="","",IF(K162&lt;=0,"Drop",IF(J162&gt;=0.6,"Profit product",IF(J162&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
         <v/>
       </c>
       <c r="N163" s="8">
-        <f>IF(A163="","",IF(K163&lt;=0,"Drop",IF(J163&gt;=0.65,"Profit product",IF(J163&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A163="","",IF(K163&lt;=0,"Drop",IF(J163&gt;=0.6,"Profit product",IF(J163&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
         <v/>
       </c>
       <c r="N164" s="8">
-        <f>IF(A164="","",IF(K164&lt;=0,"Drop",IF(J164&gt;=0.65,"Profit product",IF(J164&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A164="","",IF(K164&lt;=0,"Drop",IF(J164&gt;=0.6,"Profit product",IF(J164&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
         <v/>
       </c>
       <c r="N165" s="8">
-        <f>IF(A165="","",IF(K165&lt;=0,"Drop",IF(J165&gt;=0.65,"Profit product",IF(J165&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A165="","",IF(K165&lt;=0,"Drop",IF(J165&gt;=0.6,"Profit product",IF(J165&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
         <v/>
       </c>
       <c r="N166" s="8">
-        <f>IF(A166="","",IF(K166&lt;=0,"Drop",IF(J166&gt;=0.65,"Profit product",IF(J166&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A166="","",IF(K166&lt;=0,"Drop",IF(J166&gt;=0.6,"Profit product",IF(J166&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
         <v/>
       </c>
       <c r="N167" s="8">
-        <f>IF(A167="","",IF(K167&lt;=0,"Drop",IF(J167&gt;=0.65,"Profit product",IF(J167&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A167="","",IF(K167&lt;=0,"Drop",IF(J167&gt;=0.6,"Profit product",IF(J167&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
         <v/>
       </c>
       <c r="N168" s="8">
-        <f>IF(A168="","",IF(K168&lt;=0,"Drop",IF(J168&gt;=0.65,"Profit product",IF(J168&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A168="","",IF(K168&lt;=0,"Drop",IF(J168&gt;=0.6,"Profit product",IF(J168&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
         <v/>
       </c>
       <c r="N169" s="8">
-        <f>IF(A169="","",IF(K169&lt;=0,"Drop",IF(J169&gt;=0.65,"Profit product",IF(J169&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A169="","",IF(K169&lt;=0,"Drop",IF(J169&gt;=0.6,"Profit product",IF(J169&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6136,7 +6136,7 @@
         <v/>
       </c>
       <c r="N170" s="8">
-        <f>IF(A170="","",IF(K170&lt;=0,"Drop",IF(J170&gt;=0.65,"Profit product",IF(J170&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A170="","",IF(K170&lt;=0,"Drop",IF(J170&gt;=0.6,"Profit product",IF(J170&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6169,7 +6169,7 @@
         <v/>
       </c>
       <c r="N171" s="8">
-        <f>IF(A171="","",IF(K171&lt;=0,"Drop",IF(J171&gt;=0.65,"Profit product",IF(J171&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A171="","",IF(K171&lt;=0,"Drop",IF(J171&gt;=0.6,"Profit product",IF(J171&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
         <v/>
       </c>
       <c r="N172" s="8">
-        <f>IF(A172="","",IF(K172&lt;=0,"Drop",IF(J172&gt;=0.65,"Profit product",IF(J172&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A172="","",IF(K172&lt;=0,"Drop",IF(J172&gt;=0.6,"Profit product",IF(J172&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6235,7 +6235,7 @@
         <v/>
       </c>
       <c r="N173" s="8">
-        <f>IF(A173="","",IF(K173&lt;=0,"Drop",IF(J173&gt;=0.65,"Profit product",IF(J173&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A173="","",IF(K173&lt;=0,"Drop",IF(J173&gt;=0.6,"Profit product",IF(J173&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6268,7 +6268,7 @@
         <v/>
       </c>
       <c r="N174" s="8">
-        <f>IF(A174="","",IF(K174&lt;=0,"Drop",IF(J174&gt;=0.65,"Profit product",IF(J174&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A174="","",IF(K174&lt;=0,"Drop",IF(J174&gt;=0.6,"Profit product",IF(J174&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6301,7 +6301,7 @@
         <v/>
       </c>
       <c r="N175" s="8">
-        <f>IF(A175="","",IF(K175&lt;=0,"Drop",IF(J175&gt;=0.65,"Profit product",IF(J175&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A175="","",IF(K175&lt;=0,"Drop",IF(J175&gt;=0.6,"Profit product",IF(J175&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
         <v/>
       </c>
       <c r="N176" s="8">
-        <f>IF(A176="","",IF(K176&lt;=0,"Drop",IF(J176&gt;=0.65,"Profit product",IF(J176&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A176="","",IF(K176&lt;=0,"Drop",IF(J176&gt;=0.6,"Profit product",IF(J176&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6367,7 +6367,7 @@
         <v/>
       </c>
       <c r="N177" s="8">
-        <f>IF(A177="","",IF(K177&lt;=0,"Drop",IF(J177&gt;=0.65,"Profit product",IF(J177&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A177="","",IF(K177&lt;=0,"Drop",IF(J177&gt;=0.6,"Profit product",IF(J177&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
         <v/>
       </c>
       <c r="N178" s="8">
-        <f>IF(A178="","",IF(K178&lt;=0,"Drop",IF(J178&gt;=0.65,"Profit product",IF(J178&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A178="","",IF(K178&lt;=0,"Drop",IF(J178&gt;=0.6,"Profit product",IF(J178&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6433,7 +6433,7 @@
         <v/>
       </c>
       <c r="N179" s="8">
-        <f>IF(A179="","",IF(K179&lt;=0,"Drop",IF(J179&gt;=0.65,"Profit product",IF(J179&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A179="","",IF(K179&lt;=0,"Drop",IF(J179&gt;=0.6,"Profit product",IF(J179&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
         <v/>
       </c>
       <c r="N180" s="8">
-        <f>IF(A180="","",IF(K180&lt;=0,"Drop",IF(J180&gt;=0.65,"Profit product",IF(J180&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A180="","",IF(K180&lt;=0,"Drop",IF(J180&gt;=0.6,"Profit product",IF(J180&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6499,7 +6499,7 @@
         <v/>
       </c>
       <c r="N181" s="8">
-        <f>IF(A181="","",IF(K181&lt;=0,"Drop",IF(J181&gt;=0.65,"Profit product",IF(J181&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A181="","",IF(K181&lt;=0,"Drop",IF(J181&gt;=0.6,"Profit product",IF(J181&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
         <v/>
       </c>
       <c r="N182" s="8">
-        <f>IF(A182="","",IF(K182&lt;=0,"Drop",IF(J182&gt;=0.65,"Profit product",IF(J182&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A182="","",IF(K182&lt;=0,"Drop",IF(J182&gt;=0.6,"Profit product",IF(J182&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6565,7 +6565,7 @@
         <v/>
       </c>
       <c r="N183" s="8">
-        <f>IF(A183="","",IF(K183&lt;=0,"Drop",IF(J183&gt;=0.65,"Profit product",IF(J183&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A183="","",IF(K183&lt;=0,"Drop",IF(J183&gt;=0.6,"Profit product",IF(J183&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6598,7 +6598,7 @@
         <v/>
       </c>
       <c r="N184" s="8">
-        <f>IF(A184="","",IF(K184&lt;=0,"Drop",IF(J184&gt;=0.65,"Profit product",IF(J184&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A184="","",IF(K184&lt;=0,"Drop",IF(J184&gt;=0.6,"Profit product",IF(J184&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
         <v/>
       </c>
       <c r="N185" s="8">
-        <f>IF(A185="","",IF(K185&lt;=0,"Drop",IF(J185&gt;=0.65,"Profit product",IF(J185&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A185="","",IF(K185&lt;=0,"Drop",IF(J185&gt;=0.6,"Profit product",IF(J185&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6664,7 +6664,7 @@
         <v/>
       </c>
       <c r="N186" s="8">
-        <f>IF(A186="","",IF(K186&lt;=0,"Drop",IF(J186&gt;=0.65,"Profit product",IF(J186&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A186="","",IF(K186&lt;=0,"Drop",IF(J186&gt;=0.6,"Profit product",IF(J186&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
         <v/>
       </c>
       <c r="N187" s="8">
-        <f>IF(A187="","",IF(K187&lt;=0,"Drop",IF(J187&gt;=0.65,"Profit product",IF(J187&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A187="","",IF(K187&lt;=0,"Drop",IF(J187&gt;=0.6,"Profit product",IF(J187&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
         <v/>
       </c>
       <c r="N188" s="8">
-        <f>IF(A188="","",IF(K188&lt;=0,"Drop",IF(J188&gt;=0.65,"Profit product",IF(J188&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A188="","",IF(K188&lt;=0,"Drop",IF(J188&gt;=0.6,"Profit product",IF(J188&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6763,7 +6763,7 @@
         <v/>
       </c>
       <c r="N189" s="8">
-        <f>IF(A189="","",IF(K189&lt;=0,"Drop",IF(J189&gt;=0.65,"Profit product",IF(J189&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A189="","",IF(K189&lt;=0,"Drop",IF(J189&gt;=0.6,"Profit product",IF(J189&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6796,7 +6796,7 @@
         <v/>
       </c>
       <c r="N190" s="8">
-        <f>IF(A190="","",IF(K190&lt;=0,"Drop",IF(J190&gt;=0.65,"Profit product",IF(J190&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A190="","",IF(K190&lt;=0,"Drop",IF(J190&gt;=0.6,"Profit product",IF(J190&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
         <v/>
       </c>
       <c r="N191" s="8">
-        <f>IF(A191="","",IF(K191&lt;=0,"Drop",IF(J191&gt;=0.65,"Profit product",IF(J191&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A191="","",IF(K191&lt;=0,"Drop",IF(J191&gt;=0.6,"Profit product",IF(J191&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6862,7 +6862,7 @@
         <v/>
       </c>
       <c r="N192" s="8">
-        <f>IF(A192="","",IF(K192&lt;=0,"Drop",IF(J192&gt;=0.65,"Profit product",IF(J192&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A192="","",IF(K192&lt;=0,"Drop",IF(J192&gt;=0.6,"Profit product",IF(J192&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
         <v/>
       </c>
       <c r="N193" s="8">
-        <f>IF(A193="","",IF(K193&lt;=0,"Drop",IF(J193&gt;=0.65,"Profit product",IF(J193&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A193="","",IF(K193&lt;=0,"Drop",IF(J193&gt;=0.6,"Profit product",IF(J193&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6928,7 +6928,7 @@
         <v/>
       </c>
       <c r="N194" s="8">
-        <f>IF(A194="","",IF(K194&lt;=0,"Drop",IF(J194&gt;=0.65,"Profit product",IF(J194&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A194="","",IF(K194&lt;=0,"Drop",IF(J194&gt;=0.6,"Profit product",IF(J194&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6961,7 +6961,7 @@
         <v/>
       </c>
       <c r="N195" s="8">
-        <f>IF(A195="","",IF(K195&lt;=0,"Drop",IF(J195&gt;=0.65,"Profit product",IF(J195&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A195="","",IF(K195&lt;=0,"Drop",IF(J195&gt;=0.6,"Profit product",IF(J195&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
         <v/>
       </c>
       <c r="N196" s="8">
-        <f>IF(A196="","",IF(K196&lt;=0,"Drop",IF(J196&gt;=0.65,"Profit product",IF(J196&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A196="","",IF(K196&lt;=0,"Drop",IF(J196&gt;=0.6,"Profit product",IF(J196&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -7027,7 +7027,7 @@
         <v/>
       </c>
       <c r="N197" s="8">
-        <f>IF(A197="","",IF(K197&lt;=0,"Drop",IF(J197&gt;=0.65,"Profit product",IF(J197&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A197="","",IF(K197&lt;=0,"Drop",IF(J197&gt;=0.6,"Profit product",IF(J197&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
         <v/>
       </c>
       <c r="N198" s="8">
-        <f>IF(A198="","",IF(K198&lt;=0,"Drop",IF(J198&gt;=0.65,"Profit product",IF(J198&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A198="","",IF(K198&lt;=0,"Drop",IF(J198&gt;=0.6,"Profit product",IF(J198&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
         <v/>
       </c>
       <c r="N199" s="8">
-        <f>IF(A199="","",IF(K199&lt;=0,"Drop",IF(J199&gt;=0.65,"Profit product",IF(J199&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A199="","",IF(K199&lt;=0,"Drop",IF(J199&gt;=0.6,"Profit product",IF(J199&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -7126,7 +7126,7 @@
         <v/>
       </c>
       <c r="N200" s="8">
-        <f>IF(A200="","",IF(K200&lt;=0,"Drop",IF(J200&gt;=0.65,"Profit product",IF(J200&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A200="","",IF(K200&lt;=0,"Drop",IF(J200&gt;=0.6,"Profit product",IF(J200&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         <v/>
       </c>
       <c r="N201" s="8">
-        <f>IF(A201="","",IF(K201&lt;=0,"Drop",IF(J201&gt;=0.65,"Profit product",IF(J201&gt;=0.5,"Traffic product","Thin"))))</f>
+        <f>IF(A201="","",IF(K201&lt;=0,"Drop",IF(J201&gt;=0.6,"Profit product",IF(J201&gt;=0.5,"Traffic product","Thin - rework"))))</f>
         <v/>
       </c>
     </row>
@@ -7190,7 +7190,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Work backwards from price: production, logistics, platform &amp; payment fees, refunds, marketing reserve → operating margin.</t>
+          <t>Work backwards from price: production, logistics, platform &amp; payment fees, refunds, marketing reserve → operating margin. Same rule as Offer Scorecard: GM ≥60% with positive consumer surplus = Profit product; 50–60% = Traffic product; below 50% = Thin (rework); no margin left = Drop.</t>
         </is>
       </c>
     </row>
